--- a/scripts/checks/results/HLR_results_09_>1_lg_families_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_09_>1_lg_families_noLgArea_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E2" t="n">
-        <v>1484</v>
+        <v>1803</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2832518542518089</v>
+        <v>0.2289660427374866</v>
       </c>
       <c r="H2" t="n">
-        <v>586.4622799559509</v>
+        <v>535.4184094840506</v>
       </c>
       <c r="I2" t="n">
-        <v>1.867790180999188e-109</v>
+        <v>6.165311118376326e-104</v>
       </c>
       <c r="J2" t="n">
-        <v>166.4167646289528</v>
+        <v>204.972863262423</v>
       </c>
       <c r="K2" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L2" t="n">
-        <v>65.76627709379278</v>
+        <v>60.86868798411442</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1121406769736879</v>
+        <v>0.113684339025193</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7273505426173328, 'N1ratio-ArgsPreds': -0.20746099596041467}</t>
+          <t>{'const': 0.5718717535467436, 'N1ratio-ArgsPreds': -2.218404205002331}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 9.29807944785156e-161, 'N1ratio-ArgsPreds': 1.867790180997848e-109}</t>
+          <t>{'const': 1.6885341073455672e-165, 'N1ratio-ArgsPreds': 6.1653111183735e-104}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5322141056490415}</t>
+          <t>{'N1ratio-ArgsPreds': -0.478503963136657}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5322141056490425)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4785039631366576)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5322141056490424)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47850396313665755)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(28.325185425181004)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.89660427374877)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E3" t="n">
-        <v>1483</v>
+        <v>1802</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2833340197018642</v>
+        <v>0.2289736207052384</v>
       </c>
       <c r="H3" t="n">
-        <v>293.1521537014121</v>
+        <v>267.5722099730518</v>
       </c>
       <c r="I3" t="n">
-        <v>5.216740544525618e-108</v>
+        <v>1.775752614386992e-102</v>
       </c>
       <c r="J3" t="n">
-        <v>166.3976872048344</v>
+        <v>204.9708487237205</v>
       </c>
       <c r="K3" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L3" t="n">
-        <v>32.89267725895557</v>
+        <v>30.43535126140843</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1122034303471574</v>
+        <v>0.1137463089476806</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7244150022829303, 'N1ratio-ArgsPreds': -0.2082249668854036, 'Fam_class': 0.00010307798138135598}</t>
+          <t>{'const': 0.5727928130395785, 'N1ratio-ArgsPreds': -2.2155869992610966, 'Fam_class': -2.6552683270416638e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 3.699520003685992e-149, 'N1ratio-ArgsPreds': 6.147673017126461e-106, 'Fam_class': 0.6801489037645043}</t>
+          <t>{'const': 2.0561756431361394e-149, 'N1ratio-ArgsPreds': 1.8133660114712908e-99, 'Fam_class': 0.8941434301697844}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5341739733374355, 'Fam_class': 0.009273970638909805}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47789629925416327, 'Fam_class': -0.0028190819687355837}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5249348997645362), 'Fam_class': np.float64(0.010706840429269778)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46929743048082667), 'Fam_class': np.float64(-0.003135015004377424)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5221095374355498), 'Fam_class': np.float64(0.00906451598571646)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4666618947829379), 'Fam_class': np.float64(-0.00275281088193429)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.259836908116377), 'Fam_class': np.float64(0.008216545005530925)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.77733240424018), 'Fam_class': np.float64(0.0007577967751695844)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>8.216545005534925e-05</v>
+        <v>7.577967751859482e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1700253197192259</v>
+        <v>0.01771080504578991</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6801489037645636</v>
+        <v>0.8941434301734381</v>
       </c>
     </row>
     <row r="4">
@@ -717,76 +717,76 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E4" t="n">
-        <v>1481</v>
+        <v>1800</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3015500493378274</v>
+        <v>0.2522330890314456</v>
       </c>
       <c r="H4" t="n">
-        <v>159.8524069784538</v>
+        <v>151.7918062423113</v>
       </c>
       <c r="I4" t="n">
-        <v>8.570536879072854e-114</v>
+        <v>5.592070480025152e-112</v>
       </c>
       <c r="J4" t="n">
-        <v>162.1682340358448</v>
+        <v>198.7875155827119</v>
       </c>
       <c r="K4" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L4" t="n">
-        <v>17.50370192172519</v>
+        <v>16.76350891595636</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1094991451963841</v>
+        <v>0.1104375086570622</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.6821348395382903, 'N1ratio-ArgsPreds': -0.19923278888480658, 'Fam_class': -0.00022407792829407593, 'Nlen_freq': -0.05523250094428789, 'Vlen_freq': 0.06243005679714495}</t>
+          <t>{'const': 0.5314127477075928, 'N1ratio-ArgsPreds': -2.1208758996412, 'Fam_class': -0.000363564911958236, 'Nlen_freq': -0.5716054623983524, 'Vlen_freq': 0.8740214270050651}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 8.273558849339648e-37, 'N1ratio-ArgsPreds': 2.3700005419089244e-97, 'Fam_class': 0.3771974790484266, 'Nlen_freq': 5.368977317321583e-06, 'Vlen_freq': 9.280941903650261e-10}</t>
+          <t>{'const': 1.0749994593490666e-59, 'N1ratio-ArgsPreds': 3.6728338575445864e-93, 'Fam_class': 0.07264341705153148, 'Nlen_freq': 3.184023050820263e-07, 'Vlen_freq': 4.087826836708915e-13}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5111057144087168, 'Fam_class': -0.0201603882805845, 'Nlen_freq': -0.1741852264184864, 'Vlen_freq': 0.23985423747447168}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4574673637071791, 'Fam_class': -0.03859946195751542, 'Nlen_freq': -0.18747118787074998, 'Vlen_freq': 0.27168002380248746}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5062760244809846), 'Fam_class': np.float64(-0.022947459349994405), 'Nlen_freq': np.float64(-0.11783500637484008), 'Vlen_freq': np.float64(0.15808761286436512)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4558527599727452), 'Fam_class': np.float64(-0.04229701688738677), 'Nlen_freq': np.float64(-0.12007655047090927), 'Vlen_freq': np.float64(0.16972779218728606)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49063736160908716), 'Fam_class': np.float64(-0.019183004624817108), 'Nlen_freq': np.float64(-0.09916952023331092), 'Vlen_freq': np.float64(0.1338016069356515)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44288479241207224), 'Fam_class': np.float64(-0.03660847964219823), 'Nlen_freq': np.float64(-0.10459117127769912), 'Vlen_freq': np.float64(0.14893042505602638)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(24.072502060672615), 'Fam_class': np.float64(0.03679876664357545), 'Nlen_freq': np.float64(0.9834593743305065), 'Vlen_freq': np.float64(1.790287001856258)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.61469393498843), 'Fam_class': np.float64(0.13401807817132425), 'Nlen_freq': np.float64(1.0939313109240993), 'Vlen_freq': np.float64(2.218027150736869)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.01821602963596314</v>
+        <v>0.02325946832620718</v>
       </c>
       <c r="V4" t="n">
-        <v>19.31272231122981</v>
+        <v>27.9947149125281</v>
       </c>
       <c r="W4" t="n">
-        <v>5.249289725085241e-09</v>
+        <v>1.064892908226383e-12</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_09_>1_lg_families_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_09_>1_lg_families_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2289660427374866</v>
+        <v>0.2230905752383499</v>
       </c>
       <c r="H2" t="n">
-        <v>535.4184094840506</v>
+        <v>517.7338494485975</v>
       </c>
       <c r="I2" t="n">
-        <v>6.165311118376326e-104</v>
+        <v>5.857522915737756e-101</v>
       </c>
       <c r="J2" t="n">
-        <v>204.972863262423</v>
+        <v>205.036942502581</v>
       </c>
       <c r="K2" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L2" t="n">
-        <v>60.86868798411442</v>
+        <v>58.87663090462121</v>
       </c>
       <c r="M2" t="n">
-        <v>0.113684339025193</v>
+        <v>0.113719879369152</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5718717535467436, 'N1ratio-ArgsPreds': -2.218404205002331}</t>
+          <t>{'const': 0.5587190655100238, 'N1ratio-ArgsPreds': -2.145662524819709}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 1.6885341073455672e-165, 'N1ratio-ArgsPreds': 6.1653111183735e-104}</t>
+          <t>{'const': 3.9637284724572447e-162, 'N1ratio-ArgsPreds': 5.857522915737049e-101}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.478503963136657}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47232465025483217}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4785039631366576)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47232465025483383)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47850396313665755)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4723246502548339)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.89660427374877)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.309057523835115)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2289736207052384</v>
+        <v>0.2231248361012059</v>
       </c>
       <c r="H3" t="n">
-        <v>267.5722099730518</v>
+        <v>258.7744938559731</v>
       </c>
       <c r="I3" t="n">
-        <v>1.775752614386992e-102</v>
+        <v>1.608663049382164e-99</v>
       </c>
       <c r="J3" t="n">
-        <v>204.9708487237205</v>
+        <v>205.0279005958367</v>
       </c>
       <c r="K3" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L3" t="n">
-        <v>30.43535126140843</v>
+        <v>29.4428364056828</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1137463089476806</v>
+        <v>0.1137779692540714</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5727928130395785, 'N1ratio-ArgsPreds': -2.2155869992610966, 'Fam_class': -2.6552683270416638e-05}</t>
+          <t>{'const': 0.560702737381192, 'N1ratio-ArgsPreds': -2.139913914280309, 'Fam_class': -5.6200300629350526e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 2.0561756431361394e-149, 'N1ratio-ArgsPreds': 1.8133660114712908e-99, 'Fam_class': 0.8941434301697844}</t>
+          <t>{'const': 5.5586834044037545e-146, 'N1ratio-ArgsPreds': 1.5706816214764862e-96, 'Fam_class': 0.7780496497473899}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47789629925416327, 'Fam_class': -0.0028190819687355837}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47105920872753443, 'Fam_class': -0.005988506083872777}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46929743048082667), 'Fam_class': np.float64(-0.003135015004377424)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4630074102758243), 'Fam_class': np.float64(-0.006640701410264955)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4666618947829379), 'Fam_class': np.float64(-0.00275281088193429)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4604220893989414), 'Fam_class': np.float64(-0.005853277958239459)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.77733240424018), 'Fam_class': np.float64(0.0007577967751695844)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.198850040648683), 'Fam_class': np.float64(0.0034260862856411883)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>7.577967751859482e-06</v>
+        <v>3.426086285607255e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01771080504578991</v>
+        <v>0.0794697497559409</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8941434301734381</v>
+        <v>0.778049649751871</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2522330890314456</v>
+        <v>0.2482309731972496</v>
       </c>
       <c r="H4" t="n">
-        <v>151.7918062423113</v>
+        <v>148.5881087889928</v>
       </c>
       <c r="I4" t="n">
-        <v>5.592070480025152e-112</v>
+        <v>6.714657488377373e-110</v>
       </c>
       <c r="J4" t="n">
-        <v>198.7875155827119</v>
+        <v>198.4020502403687</v>
       </c>
       <c r="K4" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L4" t="n">
-        <v>16.76350891595636</v>
+        <v>16.3778807917084</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1104375086570622</v>
+        <v>0.1102233612446493</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5314127477075928, 'N1ratio-ArgsPreds': -2.1208758996412, 'Fam_class': -0.000363564911958236, 'Nlen_freq': -0.5716054623983524, 'Vlen_freq': 0.8740214270050651}</t>
+          <t>{'const': 0.5241243768925983, 'N1ratio-ArgsPreds': -2.045266750179362, 'Fam_class': -0.0003971644610905882, 'Nlen_freq': -0.6090982644228096, 'Vlen_freq': 0.9073491700629541}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.0749994593490666e-59, 'N1ratio-ArgsPreds': 3.6728338575445864e-93, 'Fam_class': 0.07264341705153148, 'Nlen_freq': 3.184023050820263e-07, 'Vlen_freq': 4.087826836708915e-13}</t>
+          <t>{'const': 1.7962552026478266e-58, 'N1ratio-ArgsPreds': 2.5232612414863067e-90, 'Fam_class': 0.049433445503326234, 'Nlen_freq': 4.491969806024097e-08, 'Vlen_freq': 3.969387623079432e-14}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4574673637071791, 'Fam_class': -0.03859946195751542, 'Nlen_freq': -0.18747118787074998, 'Vlen_freq': 0.27168002380248746}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4502245303172621, 'Fam_class': -0.04232044606353783, 'Nlen_freq': -0.20072219793588678, 'Vlen_freq': 0.2834815912212985}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4558527599727452), 'Fam_class': np.float64(-0.04229701688738677), 'Nlen_freq': np.float64(-0.12007655047090927), 'Vlen_freq': np.float64(0.16972779218728606)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44949228138581804), 'Fam_class': np.float64(-0.04629318353540657), 'Nlen_freq': np.float64(-0.12842055630716992), 'Vlen_freq': np.float64(0.17685572745528377)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44288479241207224), 'Fam_class': np.float64(-0.03660847964219823), 'Nlen_freq': np.float64(-0.10459117127769912), 'Vlen_freq': np.float64(0.14893042505602638)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4362895320230319), 'Fam_class': np.float64(-0.04018140522118025), 'Nlen_freq': np.float64(-0.1122762185706483), 'Vlen_freq': np.float64(0.15579795408537883)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.61469393498843), 'Fam_class': np.float64(0.13401807817132425), 'Nlen_freq': np.float64(1.0939313109240993), 'Vlen_freq': np.float64(2.218027150736869)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.03485557528762), 'Fam_class': np.float64(0.16145453255486916), 'Nlen_freq': np.float64(1.2605949256523992), 'Vlen_freq': np.float64(2.4273002497189813)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.02325946832620718</v>
+        <v>0.0251061370960437</v>
       </c>
       <c r="V4" t="n">
-        <v>27.9947149125281</v>
+        <v>30.05647024663595</v>
       </c>
       <c r="W4" t="n">
-        <v>1.064892908226383e-12</v>
+        <v>1.445013554126184e-13</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_09_>1_lg_families_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_09_>1_lg_families_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2230905752383499</v>
+        <v>0.2229212985647023</v>
       </c>
       <c r="H2" t="n">
-        <v>517.7338494485975</v>
+        <v>517.2283072097867</v>
       </c>
       <c r="I2" t="n">
-        <v>5.857522915737756e-101</v>
+        <v>7.131389721807892e-101</v>
       </c>
       <c r="J2" t="n">
-        <v>205.036942502581</v>
+        <v>205.0816169144178</v>
       </c>
       <c r="K2" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L2" t="n">
-        <v>58.87663090462121</v>
+        <v>58.8319564927844</v>
       </c>
       <c r="M2" t="n">
-        <v>0.113719879369152</v>
+        <v>0.1137446571904702</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5587190655100238, 'N1ratio-ArgsPreds': -2.145662524819709}</t>
+          <t>{'const': 0.5582554068474909, 'N1ratio-ArgsPreds': -2.1419111097183157}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.9637284724572447e-162, 'N1ratio-ArgsPreds': 5.857522915737049e-101}</t>
+          <t>{'const': 4.624050485653135e-162, 'N1ratio-ArgsPreds': 7.131389721806646e-101}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47232465025483217}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47214542099304796}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47232465025483383)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47214542099304907)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4723246502548339)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47214542099304924)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.309057523835115)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.292129856470368)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2231248361012059</v>
+        <v>0.2229547310752517</v>
       </c>
       <c r="H3" t="n">
-        <v>258.7744938559731</v>
+        <v>258.5206045675775</v>
       </c>
       <c r="I3" t="n">
-        <v>1.608663049382164e-99</v>
+        <v>1.959452906202537e-99</v>
       </c>
       <c r="J3" t="n">
-        <v>205.0279005958367</v>
+        <v>205.0727936210907</v>
       </c>
       <c r="K3" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L3" t="n">
-        <v>29.4428364056828</v>
+        <v>29.42038989305573</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1137779692540714</v>
+        <v>0.1138028821426697</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.560702737381192, 'N1ratio-ArgsPreds': -2.139913914280309, 'Fam_class': -5.6200300629350526e-05}</t>
+          <t>{'const': 0.5602148077775055, 'N1ratio-ArgsPreds': -2.1362337844613317, 'Fam_class': -5.5519547741680146e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 5.5586834044037545e-146, 'N1ratio-ArgsPreds': 1.5706816214764862e-96, 'Fam_class': 0.7780496497473899}</t>
+          <t>{'const': 6.8348741435208885e-146, 'N1ratio-ArgsPreds': 1.9139532586621353e-96, 'Fam_class': 0.7807030687217626}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47105920872753443, 'Fam_class': -0.005988506083872777}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47089395770336656, 'Fam_class': -0.005915967453940628}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4630074102758243), 'Fam_class': np.float64(-0.006640701410264955)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46282160846745146), 'Fam_class': np.float64(-0.00655921689850517)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4604220893989414), 'Fam_class': np.float64(-0.005853277958239459)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4602373250623426), 'Fam_class': np.float64(-0.005782085311498247)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.198850040648683), 'Fam_class': np.float64(0.0034260862856411883)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.181839538054042), 'Fam_class': np.float64(0.0033432510549443774)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>3.426086285607255e-05</v>
+        <v>3.343251054932495e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0794697497559409</v>
+        <v>0.07753136968873034</v>
       </c>
       <c r="W3" t="n">
-        <v>0.778049649751871</v>
+        <v>0.7807030687255732</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2482309731972496</v>
+        <v>0.2480779158945364</v>
       </c>
       <c r="H4" t="n">
-        <v>148.5881087889928</v>
+        <v>148.4662633434286</v>
       </c>
       <c r="I4" t="n">
-        <v>6.714657488377373e-110</v>
+        <v>8.05986414359035e-110</v>
       </c>
       <c r="J4" t="n">
-        <v>198.4020502403687</v>
+        <v>198.4424441400637</v>
       </c>
       <c r="K4" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L4" t="n">
-        <v>16.3778807917084</v>
+        <v>16.36778231678462</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1102233612446493</v>
+        <v>0.1102458023000354</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5241243768925983, 'N1ratio-ArgsPreds': -2.045266750179362, 'Fam_class': -0.0003971644610905882, 'Nlen_freq': -0.6090982644228096, 'Vlen_freq': 0.9073491700629541}</t>
+          <t>{'const': 0.5240538858352772, 'N1ratio-ArgsPreds': -2.041487761449064, 'Fam_class': -0.00039614652535123013, 'Nlen_freq': -0.618750858942273, 'Vlen_freq': 0.9081858899730286}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.7962552026478266e-58, 'N1ratio-ArgsPreds': 2.5232612414863067e-90, 'Fam_class': 0.049433445503326234, 'Nlen_freq': 4.491969806024097e-08, 'Vlen_freq': 3.969387623079432e-14}</t>
+          <t>{'const': 1.7036489058745053e-58, 'N1ratio-ArgsPreds': 3.2443362124485103e-90, 'Fam_class': 0.050055339390773564, 'Nlen_freq': 4.08333654963805e-08, 'Vlen_freq': 3.8043154951495046e-14}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4502245303172621, 'Fam_class': -0.04232044606353783, 'Nlen_freq': -0.20072219793588678, 'Vlen_freq': 0.2834815912212985}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4500089169005168, 'Fam_class': -0.04221197841657025, 'Nlen_freq': -0.20141774176095825, 'Vlen_freq': 0.28379693763058167}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44949228138581804), 'Fam_class': np.float64(-0.04629318353540657), 'Nlen_freq': np.float64(-0.12842055630716992), 'Vlen_freq': np.float64(0.17685572745528377)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4492448179631534), 'Fam_class': np.float64(-0.04616742530894761), 'Nlen_freq': np.float64(-0.1288134935868273), 'Vlen_freq': np.float64(0.1769828198042687)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4362895320230319), 'Fam_class': np.float64(-0.04018140522118025), 'Nlen_freq': np.float64(-0.1122762185706483), 'Vlen_freq': np.float64(0.15579795408537883)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.436032963179477), 'Fam_class': np.float64(-0.040076095584455074), 'Nlen_freq': np.float64(-0.11263700989340962), 'Vlen_freq': np.float64(0.155929403719172)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.03485557528762), 'Fam_class': np.float64(0.16145453255486916), 'Nlen_freq': np.float64(1.2605949256523992), 'Vlen_freq': np.float64(2.4273002497189813)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.012474497907515), 'Fam_class': np.float64(0.16060934372943794), 'Nlen_freq': np.float64(1.2687095997728057), 'Vlen_freq': np.float64(2.4313978944216528)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.0251061370960437</v>
+        <v>0.02512318481928477</v>
       </c>
       <c r="V4" t="n">
-        <v>30.05647024663595</v>
+        <v>30.07075708416741</v>
       </c>
       <c r="W4" t="n">
-        <v>1.445013554126184e-13</v>
+        <v>1.425173663460252e-13</v>
       </c>
     </row>
   </sheetData>
